--- a/artfynd/A 17649-2019 artfynd.xlsx
+++ b/artfynd/A 17649-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126067931</v>
       </c>
       <c r="B2" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126067929</v>
       </c>
       <c r="B3" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17649-2019 artfynd.xlsx
+++ b/artfynd/A 17649-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126067931</v>
       </c>
       <c r="B2" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126067929</v>
       </c>
       <c r="B3" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17649-2019 artfynd.xlsx
+++ b/artfynd/A 17649-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126067931</v>
       </c>
       <c r="B2" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126067929</v>
       </c>
       <c r="B3" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17649-2019 artfynd.xlsx
+++ b/artfynd/A 17649-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126067931</v>
       </c>
       <c r="B2" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126067929</v>
       </c>
       <c r="B3" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17649-2019 artfynd.xlsx
+++ b/artfynd/A 17649-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126067931</v>
       </c>
       <c r="B2" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126067929</v>
       </c>
       <c r="B3" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17649-2019 artfynd.xlsx
+++ b/artfynd/A 17649-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126067931</v>
       </c>
       <c r="B2" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126067929</v>
       </c>
       <c r="B3" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17649-2019 artfynd.xlsx
+++ b/artfynd/A 17649-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126067931</v>
       </c>
       <c r="B2" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126067929</v>
       </c>
       <c r="B3" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
